--- a/dados/produtos.xlsx
+++ b/dados/produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>ccccccccc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -603,19 +603,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Teclado</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Periférico</t>
+          <t>testeaaa</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>180</v>
+        <v>2999.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aaaaa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bbbbb</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" t="n">
+        <v>19.99</v>
       </c>
     </row>
   </sheetData>

--- a/dados/produtos.xlsx
+++ b/dados/produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ccccccccc</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -603,37 +603,379 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t>Teclado</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>testeaaa</t>
+          <t>Periférico</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>2999.99</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aaaaa</t>
+          <t>Impressora</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bbbbb</t>
+          <t>Impressão</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>19.99</v>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Computador</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Celular</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Computador</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Microfone</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Áudio</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Caixa de Som</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Áudio</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Armazenamento</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HD Externo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Armazenamento</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pen Drive</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Armazenamento</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Roteador</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rede</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rede</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Computador</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Periférico</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Teclado</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Periférico</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Headset</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Áudio</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Webcam</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Câmera</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Impressora</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Impressão</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Computador</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Armazenamento</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Roteador</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rede</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>280</v>
       </c>
     </row>
   </sheetData>
